--- a/entrepreneur_forms/023_laptop_research_survey--entrepreneur_forms.xlsx
+++ b/entrepreneur_forms/023_laptop_research_survey--entrepreneur_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>laptop_portability</t>
+          <t>laptop_portability_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>How portable do you want your laptop to be?</t>
+          <t>Laptop Portability 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>laptop_size</t>
+          <t>laptop_size_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>What is your laptop size preference?</t>
+          <t>Laptop Size 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>laptop_color</t>
+          <t>laptop_color_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>What is your laptop color preference?</t>
+          <t>Laptop Color 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>What is your budget for a laptop?</t>
+          <t>Laptop Cost</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>laptop_warranty</t>
+          <t>laptop_warranty_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Do you want a laptop with warranty?</t>
+          <t>Laptop Warranty 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1658,7 +1658,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>laptop_portability_choices</t>
+          <t>laptop_portability_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1675,7 +1675,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>laptop_portability_choices</t>
+          <t>laptop_portability_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1692,7 +1692,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>laptop_portability_choices</t>
+          <t>laptop_portability_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1709,7 +1709,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>laptop_size_choices</t>
+          <t>laptop_size_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1726,7 +1726,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>laptop_size_choices</t>
+          <t>laptop_size_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1743,7 +1743,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>laptop_size_choices</t>
+          <t>laptop_size_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1760,7 +1760,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>laptop_size_choices</t>
+          <t>laptop_size_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1777,7 +1777,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>laptop_color_choices</t>
+          <t>laptop_color_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1794,7 +1794,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>laptop_color_choices</t>
+          <t>laptop_color_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1811,7 +1811,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>laptop_color_choices</t>
+          <t>laptop_color_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1828,7 +1828,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>laptop_color_choices</t>
+          <t>laptop_color_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1845,7 +1845,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>laptop_warranty_choices</t>
+          <t>laptop_warranty_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1862,7 +1862,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>laptop_warranty_choices</t>
+          <t>laptop_warranty_2_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
